--- a/configuration-example.xlsx
+++ b/configuration-example.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kelvin\go\file-transfer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32A20F81-1143-40AF-9587-454C9774102A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="File Transfers" sheetId="1" r:id="rId1"/>
     <sheet name="File Checks" sheetId="2" r:id="rId2"/>
+    <sheet name="File Check Rules" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Source Path</t>
   </si>
@@ -64,21 +64,66 @@
   <si>
     <t>D:\Reports\Daily\previous.xlsx</t>
   </si>
+  <si>
+    <t>Check ID</t>
+  </si>
+  <si>
+    <t>CHK-001</t>
+  </si>
+  <si>
+    <t>CHK-002</t>
+  </si>
+  <si>
+    <t>CHK-003</t>
+  </si>
+  <si>
+    <t>Rule ID</t>
+  </si>
+  <si>
+    <t>Rule Name</t>
+  </si>
+  <si>
+    <t>Rule Type</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Anchor</t>
+  </si>
+  <si>
+    <t>Parent Direction</t>
+  </si>
+  <si>
+    <t>Header Depth</t>
+  </si>
+  <si>
+    <t>Require Order</t>
+  </si>
+  <si>
+    <t>Expected Text</t>
+  </si>
+  <si>
+    <t>Rule Config</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="2">
     <font>
+      <name val="Carlito"/>
       <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
-      <b/>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -108,18 +153,18 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -132,7 +177,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT">
   <a:themeElements>
     <a:clrScheme name="ChatGPT">
       <a:dk1>
@@ -281,13 +326,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="42"/>
+    <col customWidth="true" max="2" min="2" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="26.45" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -295,7 +340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="52.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="52.7" customHeight="true">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -303,7 +348,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="52.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="52.7" customHeight="true">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -311,7 +356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="26.45" customHeight="true">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -327,45 +372,89 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col customWidth="true" max="2" min="2" width="42"/>
+    <col customWidth="true" max="3" min="3" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="15" customHeight="true">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="52.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="52.7" customHeight="true">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" ht="66" customHeight="true">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="52.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" ht="52.7" customHeight="true">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="5" min="1" width="18"/>
+    <col customWidth="true" max="6" min="6" width="72"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/configuration-example.xlsx
+++ b/configuration-example.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Source Path</t>
   </si>
@@ -108,6 +108,57 @@
   </si>
   <si>
     <t>Rule Config</t>
+  </si>
+  <si>
+    <t>SAMPLE-DEMO</t>
+  </si>
+  <si>
+    <t>sample/sample_file_05_31_2026.xlsx</t>
+  </si>
+  <si>
+    <t>sample/sample_file_04_30_2026.xlsx</t>
+  </si>
+  <si>
+    <t>TXT-001</t>
+  </si>
+  <si>
+    <t>Find sample text</t>
+  </si>
+  <si>
+    <t>exact_text</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>{"sheet":"Report","expected_text":"sometypeofTextthatneeds to be serached"}</t>
+  </si>
+  <si>
+    <t>HDR-001</t>
+  </si>
+  <si>
+    <t>Headers around date anchor</t>
+  </si>
+  <si>
+    <t>header_compare</t>
+  </si>
+  <si>
+    <t>{"sheet":"Report","anchor":"date","parent_direction":"up","max_header_depth":2,"require_order":true}</t>
+  </si>
+  <si>
+    <t>inception date anchor</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Compare Offset Months</t>
+  </si>
+  <si>
+    <t>sample/sample_file_{mm}_{dd}_{yyyy}.xlsx</t>
+  </si>
+  <si>
+    <t>-1</t>
   </si>
 </sst>
 </file>
@@ -374,65 +425,10 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="2" width="42"/>
-    <col customWidth="true" max="3" min="3" width="46"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="true">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="52.7" customHeight="true">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="66" customHeight="true">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="52.7" customHeight="true">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="5" min="1" width="18"/>
-    <col customWidth="true" max="6" min="6" width="72"/>
+    <col customWidth="true" max="1" min="1" width="24"/>
+    <col customWidth="true" max="2" min="2" width="54"/>
+    <col customWidth="true" max="3" min="3" width="24"/>
+    <col customWidth="true" max="6" min="4" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,6 +436,41 @@
         <v>14</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="5" min="1" width="20"/>
+    <col customWidth="true" max="6" min="6" width="96"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
       <c r="C1" t="s">
@@ -453,6 +484,46 @@
       </c>
       <c r="F1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/configuration-example.xlsx
+++ b/configuration-example.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Source Path</t>
   </si>
@@ -159,6 +159,24 @@
   </si>
   <si>
     <t>-1</t>
+  </si>
+  <si>
+    <t>{"sheet":"Report","anchor":"date","parent_direction":"up","max_header_depth":3,"require_order":true}</t>
+  </si>
+  <si>
+    <t>SCAN-001</t>
+  </si>
+  <si>
+    <t>Reporting date scan</t>
+  </si>
+  <si>
+    <t>anchor_scan_match</t>
+  </si>
+  <si>
+    <t>{"sheet":"Report","anchor":"Reporting dates","direction":"down","select":"last_non_empty_before_blank","expected_text":"{mm}/{dd}/{yy}","compare_as":"date"}</t>
+  </si>
+  <si>
+    <t>sample/sample_file_{mm}_*_{yyyy}.xlsx</t>
   </si>
 </sst>
 </file>
@@ -447,7 +465,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
@@ -514,7 +532,7 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
@@ -523,7 +541,27 @@
         <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
